--- a/c administrativos.xlsx
+++ b/c administrativos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1A\estadisticas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA5517C1-FFD0-437E-A28F-FF2CEAF8CB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AF600A-F465-444D-A450-37BF8C510CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A893C9E9-D4FC-4CE0-BA45-549C466CCB25}"/>
+    <workbookView xWindow="0" yWindow="2304" windowWidth="23232" windowHeight="6852" xr2:uid="{A893C9E9-D4FC-4CE0-BA45-549C466CCB25}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
